--- a/templates/CAPIT D INC FIC - template.xlsx
+++ b/templates/CAPIT D INC FIC - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-15" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1252,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="2" min="1" max="1"/>
@@ -1260,8 +1260,8 @@
     <col width="5.42578125" customWidth="1" style="2" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="2" min="10" max="26"/>
-    <col width="9.140625" customWidth="1" style="2" min="27" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="10" max="27"/>
+    <col width="9.140625" customWidth="1" style="2" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -1395,96 +1395,96 @@
     <row r="16" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B16" s="36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C16" s="37" t="n">
-        <v>1.902520174141</v>
+        <v>1.935330386714</v>
       </c>
       <c r="D16" s="38" t="n">
-        <v>-0.002672134594407294</v>
+        <v>0.001243598391754475</v>
       </c>
       <c r="E16" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F16" s="39" t="n">
-        <v>-4.924120027591582</v>
+        <v>2.291661415534786</v>
       </c>
     </row>
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B17" s="40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C17" s="41" t="n">
-        <v>1.907617585083</v>
+        <v>1.9329266023</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0.001377706265349499</v>
+        <v>0.000949406059654434</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="43" t="n">
-        <v>2.53879090804205</v>
+        <v>1.74953365090435</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C18" s="41" t="n">
-        <v>1.904993064203</v>
+        <v>1.931093210704</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>-0.001894973383763765</v>
+        <v>0.005869432594310275</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>-3.49199340866805</v>
+        <v>10.81599356886166</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B19" s="40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C19" s="41" t="n">
-        <v>1.908609829029</v>
+        <v>1.919824927698</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0.003792751513190806</v>
+        <v>-0.001197547697945223</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>6.989155308594642</v>
+        <v>-2.206800741171591</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B20" s="40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>1.901398297758</v>
+        <v>1.922126766182</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>-0.004003481504855078</v>
+        <v>0.0005949241064504562</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="43" t="n">
-        <v>-7.377481470959382</v>
+        <v>1.096306194156925</v>
       </c>
     </row>
     <row r="21" ht="15.95" customHeight="1">
@@ -1524,18 +1524,18 @@
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="35">
       <c r="B23" s="44" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C23" s="44" t="inlineStr"/>
       <c r="D23" s="38" t="n">
-        <v>-0.008450207601063409</v>
+        <v>0.006876799532346434</v>
       </c>
       <c r="E23" s="38" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F23" s="39" t="n">
-        <v>-0.806058513995322</v>
+        <v>1.807388586764851</v>
       </c>
       <c r="G23" s="45" t="n"/>
     </row>
@@ -1548,13 +1548,13 @@
       </c>
       <c r="C24" s="47" t="inlineStr"/>
       <c r="D24" s="42" t="n">
-        <v>-0.005852228920723013</v>
+        <v>0.01436326503700069</v>
       </c>
       <c r="E24" s="42" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F24" s="43" t="n">
-        <v>-0.5045957971640825</v>
+        <v>1.247848818093551</v>
       </c>
       <c r="G24" s="48" t="n"/>
       <c r="H24" s="49" t="n"/>
@@ -1568,13 +1568,13 @@
       </c>
       <c r="C25" s="47" t="inlineStr"/>
       <c r="D25" s="42" t="n">
-        <v>0.0270671539728804</v>
+        <v>0.03883458088294045</v>
       </c>
       <c r="E25" s="42" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F25" s="43" t="n">
-        <v>0.7670326542564808</v>
+        <v>1.103297266359597</v>
       </c>
       <c r="G25" s="48" t="n"/>
     </row>
@@ -1587,13 +1587,13 @@
       </c>
       <c r="C26" s="47" t="inlineStr"/>
       <c r="D26" s="42" t="n">
-        <v>0.05209980285155336</v>
+        <v>0.0691160812722682</v>
       </c>
       <c r="E26" s="42" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F26" s="43" t="n">
-        <v>0.7249389285574577</v>
+        <v>0.9629520236511849</v>
       </c>
       <c r="G26" s="48" t="n"/>
     </row>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="C27" s="47" t="inlineStr"/>
       <c r="D27" s="42" t="n">
-        <v>0.1309208878736317</v>
+        <v>0.1435809399492107</v>
       </c>
       <c r="E27" s="42" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>0.8856960802174548</v>
+        <v>0.9700363796688583</v>
       </c>
       <c r="G27" s="48" t="n"/>
     </row>
@@ -1620,18 +1620,18 @@
       <c r="A28" s="50" t="n"/>
       <c r="B28" s="47" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C28" s="47" t="inlineStr"/>
       <c r="D28" s="42" t="n">
-        <v>0.02100446810840895</v>
+        <v>0.1997038128329272</v>
       </c>
       <c r="E28" s="42" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F28" s="43" t="n">
-        <v>0.6475061496151331</v>
+        <v>0.7185387538312251</v>
       </c>
       <c r="G28" s="48" t="n"/>
     </row>
@@ -1639,18 +1639,18 @@
       <c r="A29" s="50" t="n"/>
       <c r="B29" s="47" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C29" s="47" t="inlineStr"/>
       <c r="D29" s="42" t="n">
-        <v>0.146998553269345</v>
+        <v>0.03861236214913544</v>
       </c>
       <c r="E29" s="42" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="43" t="n">
-        <v>1.027008508416405</v>
+        <v>1.014635980857792</v>
       </c>
       <c r="G29" s="48" t="n"/>
     </row>
@@ -1658,18 +1658,18 @@
       <c r="A30" s="50" t="n"/>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C30" s="47" t="inlineStr"/>
       <c r="D30" s="42" t="n">
-        <v>0.04278608594473399</v>
+        <v>0.146998553269345</v>
       </c>
       <c r="E30" s="42" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F30" s="43" t="n">
-        <v>0.3917962984014792</v>
+        <v>1.027008508416405</v>
       </c>
       <c r="G30" s="48" t="n"/>
     </row>
@@ -1677,173 +1677,192 @@
       <c r="A31" s="50" t="n"/>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C31" s="47" t="inlineStr"/>
       <c r="D31" s="42" t="n">
-        <v>0.9025201741410001</v>
+        <v>0.04278608594473399</v>
       </c>
       <c r="E31" s="42" t="n">
-        <v>0.8915618232184606</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F31" s="43" t="n">
-        <v>1.012291184567528</v>
+        <v>0.3917962984014792</v>
       </c>
       <c r="G31" s="48" t="n"/>
     </row>
-    <row r="32" ht="15.95" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="26.1" customHeight="1">
+    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="35">
+      <c r="A32" s="50" t="n"/>
+      <c r="B32" s="47" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr"/>
+      <c r="D32" s="42" t="n">
+        <v>0.9353303867139999</v>
+      </c>
+      <c r="E32" s="42" t="n">
+        <v>0.9018517199827185</v>
+      </c>
+      <c r="F32" s="43" t="n">
+        <v>1.037122141023275</v>
+      </c>
+      <c r="G32" s="48" t="n"/>
+    </row>
+    <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="12" t="n"/>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B33" s="13" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="26.1" customHeight="1">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="n"/>
-      <c r="E34" s="51" t="n">
-        <v>85869917.2051</v>
-      </c>
-      <c r="F34" s="30" t="n"/>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
     <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="16" t="n"/>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="15" t="n"/>
       <c r="E35" s="51" t="n">
-        <v>110030213.3253659</v>
+        <v>86403799.1426</v>
       </c>
       <c r="F35" s="30" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="16" t="n"/>
-      <c r="B36" s="18" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="51" t="n">
+        <v>108152042.9781595</v>
+      </c>
+      <c r="F36" s="30" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="A37" s="22" t="n"/>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
+      <c r="A38" s="22" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
-      <c r="F37" s="21" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="20" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>2018-12-27</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="25" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="23" t="n"/>
       <c r="F39" s="23" t="n"/>
       <c r="G39" s="4" t="n"/>
     </row>
-    <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="32" t="inlineStr">
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="34" t="n"/>
-      <c r="C41" s="34" t="n"/>
-      <c r="D41" s="34" t="n"/>
-      <c r="E41" s="34" t="n"/>
-      <c r="F41" s="34" t="n"/>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
-      <c r="B42" s="26" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="34" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="4" t="n"/>
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="11" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="27" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="87"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="85"/>
 </worksheet>
 </file>